--- a/SGC-CKN/Excel/7decb4f8-4d91-46d9-becc-2137a1696a46_Cọc_khoan_nhồi_P7-104_D800_25-05-2026.xlsx
+++ b/SGC-CKN/Excel/7decb4f8-4d91-46d9-becc-2137a1696a46_Cọc_khoan_nhồi_P7-104_D800_25-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>23:00 22/05/2026</t>
+    <t>23:00 22/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>06:55 25/05/2026</t>
+    <t>06:55 23/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">23:00
-22/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:40
-23/05/2026</t>
+22/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:40
+22/03/2026</t>
   </si>
   <si>
     <t>Time written as 23h00 to 25h40, interpreted as 01:40 next day.</t>
@@ -115,8 +115,8 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">03:00
-23/05/2026</t>
+    <t xml:space="preserve">00:00
+23/03/2026</t>
   </si>
   <si>
     <t/>
@@ -128,12 +128,8 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
-25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50
-25/05/2026</t>
+    <t xml:space="preserve">01:50
+23/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -142,8 +138,8 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">12:45
-25/05/2026</t>
+    <t xml:space="preserve">02:25
+23/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -152,8 +148,8 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">12:55
-25/05/2026</t>
+    <t xml:space="preserve">02:55
+23/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -162,8 +158,8 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:55
-25/05/2026</t>
+    <t xml:space="preserve">03:55
+23/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -172,12 +168,8 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:55
-24/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:15
-24/05/2026</t>
+    <t xml:space="preserve">04:15
+23/03/2026</t>
   </si>
   <si>
     <t>Date written as 24/5 despite surrounding rows being 25/5.</t>
@@ -189,19 +181,15 @@
     <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">14:15
-25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:28
-25/05/2026</t>
+    <t xml:space="preserve">04:28
+23/03/2026</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">16:15
-25/05/2026</t>
+    <t xml:space="preserve">06:13
+23/03/2026</t>
   </si>
   <si>
     <t>Ghi chú: Sỏi đá</t>
@@ -213,8 +201,12 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">06:14
+23/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">06:55
-25/05/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -251,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -282,18 +274,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -350,7 +336,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -389,12 +375,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -405,11 +391,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -530,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -568,35 +549,41 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -634,22 +621,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-5.72</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.89</v>
       </c>
       <c r="H11" s="5">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="I11" s="5">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="J11" s="8">
-        <v>0.44</v>
+        <v>10.34</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1276,68 +1254,68 @@
         <v>-8.89</v>
       </c>
       <c r="H12" s="9">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
-      <c r="J12" s="12">
-        <v>1.5</v>
+      <c r="J12" s="8">
+        <v>6</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-8.89</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-17.09</v>
       </c>
-      <c r="H13" s="13">
-        <v>11.83</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>1.83</v>
+      </c>
+      <c r="I13" s="12">
         <v>8.2</v>
       </c>
-      <c r="J13" s="8">
-        <v>0.69</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="J13" s="15">
+        <v>4.47</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>41</v>
       </c>
       <c r="F14" s="16">
         <v>-17.09</v>
@@ -1346,13 +1324,13 @@
         <v>-21.39</v>
       </c>
       <c r="H14" s="16">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="I14" s="16">
         <v>4.3</v>
       </c>
-      <c r="J14" s="12">
-        <v>4.69</v>
+      <c r="J14" s="8">
+        <v>7.37</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>34</v>
@@ -1360,19 +1338,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>43</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="19">
         <v>-21.39</v>
@@ -1381,207 +1359,207 @@
         <v>-25.49</v>
       </c>
       <c r="H15" s="19">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="19">
         <v>4.1</v>
       </c>
-      <c r="J15" s="22">
-        <v>24.6</v>
+      <c r="J15" s="8">
+        <v>8.2</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="D16" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="22">
+        <v>-25.49</v>
+      </c>
+      <c r="G16" s="22">
+        <v>-35.39</v>
+      </c>
+      <c r="H16" s="22">
+        <v>1</v>
+      </c>
+      <c r="I16" s="22">
+        <v>9.9</v>
+      </c>
+      <c r="J16" s="8">
+        <v>9.9</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C17" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="25" t="s">
+      <c r="E17" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="25">
+        <v>-35.39</v>
+      </c>
+      <c r="G17" s="25">
+        <v>-37.78</v>
+      </c>
+      <c r="H17" s="25">
+        <v>0.33</v>
+      </c>
+      <c r="I17" s="25">
+        <v>2.39</v>
+      </c>
+      <c r="J17" s="8">
+        <v>7.17</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="28">
+        <v>-37.78</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-39.5</v>
+      </c>
+      <c r="H18" s="28">
+        <v>0.22</v>
+      </c>
+      <c r="I18" s="28">
+        <v>1.72</v>
+      </c>
+      <c r="J18" s="8">
+        <v>7.94</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="23">
-        <v>-25.49</v>
-      </c>
-      <c r="G16" s="23">
-        <v>-35.49</v>
-      </c>
-      <c r="H16" s="23">
-        <v>1</v>
-      </c>
-      <c r="I16" s="23">
-        <v>10</v>
-      </c>
-      <c r="J16" s="22">
-        <v>10</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="26" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="26">
-        <v>-35.49</v>
-      </c>
-      <c r="G17" s="26">
-        <v>-37.78</v>
-      </c>
-      <c r="H17" s="26">
-        <v>0.33</v>
-      </c>
-      <c r="I17" s="26">
-        <v>2.29</v>
-      </c>
-      <c r="J17" s="22">
-        <v>6.87</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="C19" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="E19" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="31">
+        <v>-39.5</v>
+      </c>
+      <c r="G19" s="31">
+        <v>-44</v>
+      </c>
+      <c r="H19" s="31">
+        <v>1.75</v>
+      </c>
+      <c r="I19" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="15">
+        <v>2.57</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="31" t="s">
+      <c r="C20" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="34">
+        <v>-44</v>
+      </c>
+      <c r="G20" s="34">
+        <v>-45.09</v>
+      </c>
+      <c r="H20" s="34">
+        <v>0.68</v>
+      </c>
+      <c r="I20" s="34">
+        <v>1.09</v>
+      </c>
+      <c r="J20" s="15">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="29">
-        <v>-37.78</v>
-      </c>
-      <c r="G18" s="29">
-        <v>-39.5</v>
-      </c>
-      <c r="H18" s="29">
-        <v>0.22</v>
-      </c>
-      <c r="I18" s="29">
-        <v>1.72</v>
-      </c>
-      <c r="J18" s="22">
-        <v>7.94</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="32">
-        <v>-39.5</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-44.52</v>
-      </c>
-      <c r="H19" s="32">
-        <v>1.78</v>
-      </c>
-      <c r="I19" s="32">
-        <v>5.02</v>
-      </c>
-      <c r="J19" s="12">
-        <v>2.81</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="35">
-        <v>-44.52</v>
-      </c>
-      <c r="G20" s="35">
-        <v>-45.09</v>
-      </c>
-      <c r="H20" s="35">
-        <v>14.67</v>
-      </c>
-      <c r="I20" s="35">
-        <v>0.57</v>
-      </c>
-      <c r="J20" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1676,31 +1654,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1717,19 +1695,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-5.72</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.89</v>
       </c>
       <c r="G2" s="5">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="H2" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="I2" s="12">
-        <v>2.44</v>
+        <v>6.89</v>
+      </c>
+      <c r="I2" s="8">
+        <v>10.34</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,42 +1730,42 @@
         <v>-8.89</v>
       </c>
       <c r="G3" s="9">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="12">
-        <v>1.5</v>
+      <c r="I3" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-8.89</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-17.09</v>
       </c>
-      <c r="G4" s="13">
-        <v>11.83</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>1.83</v>
+      </c>
+      <c r="H4" s="12">
         <v>8.2</v>
       </c>
-      <c r="I4" s="8">
-        <v>0.69</v>
+      <c r="I4" s="15">
+        <v>4.47</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1810,13 +1788,13 @@
         <v>-21.39</v>
       </c>
       <c r="G5" s="16">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="16">
         <v>4.3</v>
       </c>
-      <c r="I5" s="12">
-        <v>4.69</v>
+      <c r="I5" s="8">
+        <v>7.37</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1827,7 +1805,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1839,187 +1817,187 @@
         <v>-25.49</v>
       </c>
       <c r="G6" s="19">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="19">
         <v>4.1</v>
       </c>
-      <c r="I6" s="22">
-        <v>24.6</v>
+      <c r="I6" s="8">
+        <v>8.2</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="23">
+      <c r="C7" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-25.49</v>
       </c>
-      <c r="F7" s="23">
-        <v>-35.49</v>
-      </c>
-      <c r="G7" s="23">
+      <c r="F7" s="22">
+        <v>-35.39</v>
+      </c>
+      <c r="G7" s="22">
         <v>1</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
+        <v>9.9</v>
+      </c>
+      <c r="I7" s="8">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
+        <v>-35.39</v>
+      </c>
+      <c r="F8" s="25">
+        <v>-37.78</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.33</v>
+      </c>
+      <c r="H8" s="25">
+        <v>2.39</v>
+      </c>
+      <c r="I8" s="8">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="28">
+        <v>1</v>
+      </c>
+      <c r="E9" s="28">
+        <v>-37.78</v>
+      </c>
+      <c r="F9" s="28">
+        <v>-39.5</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.22</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.72</v>
+      </c>
+      <c r="I9" s="8">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="31">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31">
+        <v>-39.5</v>
+      </c>
+      <c r="F10" s="31">
+        <v>-44</v>
+      </c>
+      <c r="G10" s="31">
+        <v>1.75</v>
+      </c>
+      <c r="H10" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="15">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="I7" s="22">
+      <c r="B11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="34">
+        <v>1</v>
+      </c>
+      <c r="E11" s="34">
+        <v>-44</v>
+      </c>
+      <c r="F11" s="34">
+        <v>-45.09</v>
+      </c>
+      <c r="G11" s="34">
+        <v>0.68</v>
+      </c>
+      <c r="H11" s="34">
+        <v>1.09</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>7</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="26">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26">
-        <v>-35.49</v>
-      </c>
-      <c r="F8" s="26">
-        <v>-37.78</v>
-      </c>
-      <c r="G8" s="26">
-        <v>0.33</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2.29</v>
-      </c>
-      <c r="I8" s="22">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
-        <v>8</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="29">
-        <v>1</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-37.78</v>
-      </c>
-      <c r="F9" s="29">
-        <v>-39.5</v>
-      </c>
-      <c r="G9" s="29">
-        <v>0.22</v>
-      </c>
-      <c r="H9" s="29">
-        <v>1.72</v>
-      </c>
-      <c r="I9" s="22">
-        <v>7.94</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>9</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="32">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32">
-        <v>-39.5</v>
-      </c>
-      <c r="F10" s="32">
-        <v>-44.52</v>
-      </c>
-      <c r="G10" s="32">
-        <v>1.78</v>
-      </c>
-      <c r="H10" s="32">
-        <v>5.02</v>
-      </c>
-      <c r="I10" s="12">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="35">
-        <v>1</v>
-      </c>
-      <c r="E11" s="35">
-        <v>-44.52</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
         <v>-45.09</v>
       </c>
-      <c r="G11" s="35">
-        <v>14.67</v>
-      </c>
-      <c r="H11" s="35">
-        <v>0.57</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="40">
-        <v>10</v>
-      </c>
-      <c r="E12" s="40">
-        <v>-5.72</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-45.09</v>
-      </c>
-      <c r="G12" s="40">
-        <v>34.92</v>
-      </c>
-      <c r="H12" s="40">
-        <v>44.7</v>
-      </c>
-      <c r="I12" s="40">
-        <v>1.28</v>
+      <c r="G12" s="39">
+        <v>7.9</v>
+      </c>
+      <c r="H12" s="39">
+        <v>45.09</v>
+      </c>
+      <c r="I12" s="39">
+        <v>5.71</v>
       </c>
     </row>
   </sheetData>
